--- a/notebooks/data/examples/double_oreo.xlsx
+++ b/notebooks/data/examples/double_oreo.xlsx
@@ -2368,12 +2368,12 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>180° Y-axis + 180° Z-axis</t>
+          <t>180° Y-axis + 270° X-axis</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>180° Y-axis + 270° X-axis</t>
+          <t>180° Y-axis + 270° Z-axis</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>180° Y-axis + 90° Z-axis</t>
+          <t>180° Z-axis + 180° Y-axis</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
@@ -2398,77 +2398,77 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>270° X-axis + 90° Z-axis</t>
+          <t>180° Z-axis + 90° X-axis</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
+          <t>180° Z-axis + 90° Y-axis</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
           <t>270° Y-axis + 270° X-axis</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>270° Y-axis + 270° Z-axis</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>270° Y-axis + 90° X-axis</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>270° Y-axis + 90° Z-axis</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>270° Z-axis + 180° Y-axis</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <t>270° Z-axis + 270° X-axis</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>270° Z-axis + 270° Y-axis</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>270° Z-axis + 90° X-axis</t>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>270° Z-axis + 90° Y-axis</t>
-        </is>
-      </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>90° X-axis + 180° Z-axis</t>
+          <t>90° Y-axis + 270° X-axis</t>
         </is>
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t>90° X-axis + 270° Y-axis</t>
+          <t>90° Y-axis + 270° Z-axis</t>
         </is>
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>90° X-axis + 90° Z-axis</t>
+          <t>90° Y-axis + 90° X-axis</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>90° Y-axis + 180° Z-axis</t>
+          <t>90° Y-axis + 90° Z-axis</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>90° Y-axis + 270° X-axis</t>
+          <t>90° Z-axis + 180° Y-axis</t>
         </is>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
-          <t>90° Y-axis + 90° X-axis</t>
+          <t>90° Z-axis + 270° X-axis</t>
         </is>
       </c>
       <c r="AL2" s="3" t="inlineStr">
         <is>
-          <t>90° Y-axis + 90° Z-axis</t>
+          <t>90° Z-axis + 90° X-axis</t>
         </is>
       </c>
     </row>
@@ -2645,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="b">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="b">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>1</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="b">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="b">
         <v>0</v>
@@ -3471,10 +3471,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="b">
         <v>0</v>
@@ -4415,10 +4415,10 @@
         <v>1</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="b">
         <v>0</v>
@@ -4769,10 +4769,10 @@
         <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -4796,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="b">
         <v>0</v>
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="b">
         <v>0</v>
@@ -5359,10 +5359,10 @@
         <v>1</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="b">
         <v>0</v>
@@ -5477,10 +5477,10 @@
         <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="b">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="b">
         <v>0</v>
@@ -5595,10 +5595,10 @@
         <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="b">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="b">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="b">
         <v>0</v>
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="b">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="b">
         <v>0</v>
@@ -6185,10 +6185,10 @@
         <v>1</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="b">
         <v>0</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="b">
         <v>0</v>
@@ -6303,10 +6303,10 @@
         <v>1</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="b">
         <v>0</v>
@@ -6357,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="b">
         <v>0</v>
@@ -6539,10 +6539,10 @@
         <v>1</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="b">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="b">
         <v>0</v>
@@ -6593,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>1</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="b">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" t="b">
         <v>0</v>
@@ -7365,10 +7365,10 @@
         <v>1</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AA44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="b">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="b">
         <v>0</v>
@@ -7837,10 +7837,10 @@
         <v>1</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="b">
         <v>0</v>
@@ -7864,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="AA48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="b">
         <v>0</v>
@@ -7891,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK48" t="b">
         <v>0</v>
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="AA49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="b">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK49" t="b">
         <v>0</v>
@@ -8191,10 +8191,10 @@
         <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="b">
         <v>0</v>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="AA51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="b">
         <v>0</v>
@@ -8245,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK51" t="b">
         <v>0</v>
@@ -8545,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="b">
         <v>0</v>
@@ -8572,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="AA54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="b">
         <v>0</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK54" t="b">
         <v>0</v>
@@ -8663,10 +8663,10 @@
         <v>1</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="b">
         <v>0</v>
@@ -8690,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="AA55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="b">
         <v>0</v>
@@ -8717,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK55" t="b">
         <v>0</v>
@@ -9017,10 +9017,10 @@
         <v>1</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="b">
         <v>0</v>
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="AA58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="b">
         <v>0</v>
@@ -9071,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK58" t="b">
         <v>0</v>
@@ -9725,10 +9725,10 @@
         <v>1</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="b">
         <v>0</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="AA64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="b">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK64" t="b">
         <v>0</v>
@@ -9843,10 +9843,10 @@
         <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="b">
         <v>0</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="AA65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="b">
         <v>0</v>
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK65" t="b">
         <v>0</v>
@@ -9961,10 +9961,10 @@
         <v>1</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="b">
         <v>0</v>
@@ -9988,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="AA66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="b">
         <v>0</v>
@@ -10015,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK66" t="b">
         <v>0</v>
@@ -10197,10 +10197,10 @@
         <v>1</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="b">
         <v>0</v>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="AA68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="b">
         <v>0</v>
@@ -10251,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK68" t="b">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>1</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="b">
         <v>0</v>
@@ -10932,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="b">
         <v>0</v>
@@ -10959,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK74" t="b">
         <v>0</v>
